--- a/majMapping/ig/StructureDefinition-FRLMPrescriptionItem.xlsx
+++ b/majMapping/ig/StructureDefinition-FRLMPrescriptionItem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:52:25+00:00</t>
+    <t>2026-10-08T12:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/majMapping/ig/StructureDefinition-FRLMPrescriptionItem.xlsx
+++ b/majMapping/ig/StructureDefinition-FRLMPrescriptionItem.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="199">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T12:48:01+00:00</t>
+    <t>2026-10-08T13:13:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -555,6 +555,12 @@
   </si>
   <si>
     <t>Motif de non substitution (Marge thérapeutique étroite, Enfant forme galénique, Contre-indication formelle).</t>
+  </si>
+  <si>
+    <t>Valeur issue du jdv-substitution-medicament-prescripteur-cisis (1.2.250.1.213.1.1.5.860)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-substitution-medicament-prescripteur-cisis|20260916095453</t>
   </si>
   <si>
     <t>FRLMPrescriptionItem.numberOfRepeats</t>
@@ -955,7 +961,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="68.80859375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="71.01953125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="88.87109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -3939,13 +3945,13 @@
         <v>72</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>72</v>
@@ -3980,10 +3986,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4006,13 +4012,13 @@
         <v>72</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4063,7 +4069,7 @@
         <v>72</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4080,10 +4086,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4109,10 +4115,10 @@
         <v>160</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4163,7 +4169,7 @@
         <v>72</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -4180,10 +4186,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4209,10 +4215,10 @@
         <v>79</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4263,7 +4269,7 @@
         <v>72</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>73</v>
@@ -4280,10 +4286,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4306,13 +4312,13 @@
         <v>72</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4363,7 +4369,7 @@
         <v>72</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>73</v>
@@ -4380,10 +4386,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4409,10 +4415,10 @@
         <v>142</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4463,7 +4469,7 @@
         <v>72</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -4480,10 +4486,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4506,13 +4512,13 @@
         <v>72</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4563,7 +4569,7 @@
         <v>72</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -4580,10 +4586,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4606,13 +4612,13 @@
         <v>72</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4663,7 +4669,7 @@
         <v>72</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>73</v>
@@ -4680,10 +4686,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4706,13 +4712,13 @@
         <v>72</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4763,7 +4769,7 @@
         <v>72</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>73</v>
@@ -4780,10 +4786,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4806,13 +4812,13 @@
         <v>72</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4863,7 +4869,7 @@
         <v>72</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>73</v>
@@ -4880,10 +4886,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4906,13 +4912,13 @@
         <v>72</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4963,7 +4969,7 @@
         <v>72</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>73</v>
